--- a/fiyat_listesi.xlsx
+++ b/fiyat_listesi.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E4EB4C-1F36-484F-BE08-809D228B1D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -370,7 +371,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₺&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₺&quot;;[Red]#,##0.00\ &quot;₺&quot;"/>
@@ -437,9 +438,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,9 +459,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Teması">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -498,9 +499,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -535,7 +536,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -570,7 +571,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -743,18 +744,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -788,13 +789,13 @@
         <v>1058.3999999999999</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -808,13 +809,13 @@
         <v>1323</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -828,13 +829,13 @@
         <v>1531.44</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -848,13 +849,13 @@
         <v>1786.6799999999998</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -868,13 +869,13 @@
         <v>1872.96</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -888,13 +889,13 @@
         <v>2107.08</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -908,13 +909,13 @@
         <v>2341.1999999999998</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -928,13 +929,13 @@
         <v>2575.3200000000002</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -948,13 +949,13 @@
         <v>2640.9599999999996</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -968,13 +969,13 @@
         <v>2861.0400000000004</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -988,13 +989,13 @@
         <v>3081.12</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1008,13 +1009,13 @@
         <v>3301.2</v>
       </c>
       <c r="E13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1028,13 +1029,13 @@
         <v>3408</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1048,13 +1049,13 @@
         <v>3621</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1068,13 +1069,13 @@
         <v>3834</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1088,13 +1089,13 @@
         <v>4047</v>
       </c>
       <c r="E17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F17">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1108,13 +1109,13 @@
         <v>4260</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1128,13 +1129,13 @@
         <v>4635.84</v>
       </c>
       <c r="E19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1148,13 +1149,13 @@
         <v>5057.28</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1168,13 +1169,13 @@
         <v>5478.72</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F21">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1188,13 +1189,13 @@
         <v>5900.1599999999989</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F22">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1208,13 +1209,13 @@
         <v>6321.5999999999995</v>
       </c>
       <c r="E23">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F23">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1228,13 +1229,13 @@
         <v>1187.04</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1248,13 +1249,13 @@
         <v>1483.8</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F25">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1268,13 +1269,13 @@
         <v>1717.9199999999998</v>
       </c>
       <c r="E26">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F26">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1288,13 +1289,13 @@
         <v>2004.2399999999998</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F27">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1308,13 +1309,13 @@
         <v>2101.44</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F28">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1328,13 +1329,13 @@
         <v>2364.12</v>
       </c>
       <c r="E29">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F29">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1348,13 +1349,13 @@
         <v>2626.7999999999997</v>
       </c>
       <c r="E30">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F30">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1368,13 +1369,13 @@
         <v>2889.48</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F31">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1388,13 +1389,13 @@
         <v>2962.08</v>
       </c>
       <c r="E32">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F32">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1408,13 +1409,13 @@
         <v>3208.9199999999996</v>
       </c>
       <c r="E33">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1428,13 +1429,13 @@
         <v>3455.7599999999998</v>
       </c>
       <c r="E34">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F34">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1448,13 +1449,13 @@
         <v>3702.6</v>
       </c>
       <c r="E35">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F35">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -1468,13 +1469,13 @@
         <v>3824.6400000000003</v>
       </c>
       <c r="E36">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F36">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -1488,13 +1489,13 @@
         <v>4063.68</v>
       </c>
       <c r="E37">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F37">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -1508,13 +1509,13 @@
         <v>4302.7199999999993</v>
       </c>
       <c r="E38">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F38">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -1528,13 +1529,13 @@
         <v>4541.7599999999993</v>
       </c>
       <c r="E39">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F39">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1548,13 +1549,13 @@
         <v>4780.8</v>
       </c>
       <c r="E40">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F40">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -1568,13 +1569,13 @@
         <v>5200.8</v>
       </c>
       <c r="E41">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F41">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -1588,13 +1589,13 @@
         <v>5673.5999999999995</v>
       </c>
       <c r="E42">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F42">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -1608,13 +1609,13 @@
         <v>6146.4</v>
       </c>
       <c r="E43">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F43">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -1628,13 +1629,13 @@
         <v>6619.2</v>
       </c>
       <c r="E44">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F44">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -1648,13 +1649,13 @@
         <v>7092</v>
       </c>
       <c r="E45">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F45">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -1668,13 +1669,13 @@
         <v>1432.3200000000002</v>
       </c>
       <c r="E46">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F46">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -1688,13 +1689,13 @@
         <v>1790.3999999999999</v>
       </c>
       <c r="E47">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F47">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -1708,13 +1709,13 @@
         <v>2072.16</v>
       </c>
       <c r="E48">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F48">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -1728,13 +1729,13 @@
         <v>2417.52</v>
       </c>
       <c r="E49">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F49">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -1748,13 +1749,13 @@
         <v>2535.36</v>
       </c>
       <c r="E50">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F50">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -1768,13 +1769,13 @@
         <v>2852.28</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F51">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -1788,13 +1789,13 @@
         <v>3169.2</v>
       </c>
       <c r="E52">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F52">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -1808,13 +1809,13 @@
         <v>3486.1200000000003</v>
       </c>
       <c r="E53">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F53">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1828,13 +1829,13 @@
         <v>3574.08</v>
       </c>
       <c r="E54">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F54">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1848,13 +1849,13 @@
         <v>3871.9199999999996</v>
       </c>
       <c r="E55">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F55">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -1868,13 +1869,13 @@
         <v>4169.7599999999993</v>
       </c>
       <c r="E56">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F56">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -1888,13 +1889,13 @@
         <v>4467.5999999999995</v>
       </c>
       <c r="E57">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F57">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1908,13 +1909,13 @@
         <v>4613.76</v>
       </c>
       <c r="E58">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F58">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -1928,13 +1929,13 @@
         <v>4902.12</v>
       </c>
       <c r="E59">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F59">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1948,13 +1949,13 @@
         <v>5190.4800000000005</v>
       </c>
       <c r="E60">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F60">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1968,13 +1969,13 @@
         <v>5478.8399999999992</v>
       </c>
       <c r="E61">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F61">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -1988,13 +1989,13 @@
         <v>5767.2</v>
       </c>
       <c r="E62">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F62">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -2008,13 +2009,13 @@
         <v>6275.2800000000007</v>
       </c>
       <c r="E63">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F63">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -2028,13 +2029,13 @@
         <v>6845.76</v>
       </c>
       <c r="E64">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F64">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -2048,13 +2049,13 @@
         <v>7416.24</v>
       </c>
       <c r="E65">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -2068,13 +2069,13 @@
         <v>7986.7199999999993</v>
       </c>
       <c r="E66">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F66">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -2088,13 +2089,13 @@
         <v>8557.1999999999989</v>
       </c>
       <c r="E67">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F67">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -2108,13 +2109,13 @@
         <v>1627.2</v>
       </c>
       <c r="E68">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F68">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2128,13 +2129,13 @@
         <v>2034</v>
       </c>
       <c r="E69">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F69">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -2148,13 +2149,13 @@
         <v>2354.4</v>
       </c>
       <c r="E70">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F70">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -2168,13 +2169,13 @@
         <v>2746.7999999999997</v>
       </c>
       <c r="E71">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F71">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2188,13 +2189,13 @@
         <v>2880</v>
       </c>
       <c r="E72">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F72">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2208,13 +2209,13 @@
         <v>3240</v>
       </c>
       <c r="E73">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F73">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -2228,13 +2229,13 @@
         <v>3600</v>
       </c>
       <c r="E74">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F74">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2248,13 +2249,13 @@
         <v>3960.0000000000005</v>
       </c>
       <c r="E75">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F75">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2268,13 +2269,13 @@
         <v>4060.7999999999997</v>
       </c>
       <c r="E76">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F76">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2288,13 +2289,13 @@
         <v>4399.2</v>
       </c>
       <c r="E77">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2308,13 +2309,13 @@
         <v>4737.5999999999995</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F78">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2328,13 +2329,13 @@
         <v>5076</v>
       </c>
       <c r="E79">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F79">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -2348,13 +2349,13 @@
         <v>5241.5999999999995</v>
       </c>
       <c r="E80">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F80">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -2368,13 +2369,13 @@
         <v>5569.2</v>
       </c>
       <c r="E81">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F81">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -2388,13 +2389,13 @@
         <v>5896.8</v>
       </c>
       <c r="E82">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F82">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -2408,13 +2409,13 @@
         <v>6224.4</v>
       </c>
       <c r="E83">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F83">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -2428,13 +2429,13 @@
         <v>6552</v>
       </c>
       <c r="E84">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F84">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -2448,13 +2449,13 @@
         <v>7128.0000000000009</v>
       </c>
       <c r="E85">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F85">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2468,13 +2469,13 @@
         <v>7776</v>
       </c>
       <c r="E86">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F86">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -2488,13 +2489,13 @@
         <v>8424</v>
       </c>
       <c r="E87">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F87">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -2508,13 +2509,13 @@
         <v>9071.9999999999982</v>
       </c>
       <c r="E88">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F88">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -2528,13 +2529,13 @@
         <v>9720</v>
       </c>
       <c r="E89">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F89">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -2548,13 +2549,13 @@
         <v>2278.08</v>
       </c>
       <c r="E90">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F90">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -2568,13 +2569,13 @@
         <v>2847.6</v>
       </c>
       <c r="E91">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F91">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -2588,13 +2589,13 @@
         <v>3296.1599999999994</v>
       </c>
       <c r="E92">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F92">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -2608,13 +2609,13 @@
         <v>3845.5199999999995</v>
       </c>
       <c r="E93">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F93">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>6</v>
       </c>
@@ -2628,13 +2629,13 @@
         <v>4032</v>
       </c>
       <c r="E94">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F94">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2648,13 +2649,13 @@
         <v>4536</v>
       </c>
       <c r="E95">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F95">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>6</v>
       </c>
@@ -2668,13 +2669,13 @@
         <v>5040</v>
       </c>
       <c r="E96">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F96">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -2688,13 +2689,13 @@
         <v>5544</v>
       </c>
       <c r="E97">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F97">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -2708,13 +2709,13 @@
         <v>5685.119999999999</v>
       </c>
       <c r="E98">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F98">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -2728,13 +2729,13 @@
         <v>6158.88</v>
       </c>
       <c r="E99">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F99">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>6</v>
       </c>
@@ -2748,13 +2749,13 @@
         <v>6632.6399999999994</v>
       </c>
       <c r="E100">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F100">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -2768,13 +2769,13 @@
         <v>7106.4</v>
       </c>
       <c r="E101">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F101">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -2788,13 +2789,13 @@
         <v>7338.2400000000007</v>
       </c>
       <c r="E102">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F102">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>6</v>
       </c>
@@ -2808,13 +2809,13 @@
         <v>7796.8799999999992</v>
       </c>
       <c r="E103">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F103">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -2828,13 +2829,13 @@
         <v>8255.52</v>
       </c>
       <c r="E104">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F104">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -2848,13 +2849,13 @@
         <v>8714.159999999998</v>
       </c>
       <c r="E105">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F105">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>6</v>
       </c>
@@ -2868,13 +2869,13 @@
         <v>9172.7999999999993</v>
       </c>
       <c r="E106">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F106">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>6</v>
       </c>
@@ -2888,13 +2889,13 @@
         <v>9979.1999999999989</v>
       </c>
       <c r="E107">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F107">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>6</v>
       </c>
@@ -2908,13 +2909,13 @@
         <v>10886.4</v>
       </c>
       <c r="E108">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F108">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -2928,13 +2929,13 @@
         <v>11793.6</v>
       </c>
       <c r="E109">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F109">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -2948,13 +2949,13 @@
         <v>12700.8</v>
       </c>
       <c r="E110">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F110">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -2968,10 +2969,10 @@
         <v>13608</v>
       </c>
       <c r="E111">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F111">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
